--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31491,6 +31491,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1354" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31514,6 +31514,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1355" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1355" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31537,6 +31537,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1356" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31560,6 +31560,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1357" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31424,7 +31424,7 @@
     </row>
     <row r="1351">
       <c r="A1351" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1351" t="n">
         <v>0</v>
@@ -31447,7 +31447,7 @@
     </row>
     <row r="1352">
       <c r="A1352" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1352" t="n">
         <v>0</v>
@@ -31470,7 +31470,7 @@
     </row>
     <row r="1353">
       <c r="A1353" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1353" t="n">
         <v>0</v>
@@ -31493,7 +31493,7 @@
     </row>
     <row r="1354">
       <c r="A1354" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1354" t="n">
         <v>0</v>
@@ -31516,7 +31516,7 @@
     </row>
     <row r="1355">
       <c r="A1355" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1355" t="n">
         <v>0</v>
@@ -31539,7 +31539,7 @@
     </row>
     <row r="1356">
       <c r="A1356" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1356" t="n">
         <v>0</v>
@@ -31562,24 +31562,47 @@
     </row>
     <row r="1357">
       <c r="A1357" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1357" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1357" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1357" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D1357" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E1357" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F1357" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G1357" t="s">
+      <c r="B1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1358" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31606,6 +31606,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1359" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1359" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1360" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31652,6 +31652,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1361" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31675,6 +31675,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1362" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31698,6 +31698,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1363" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31721,6 +31721,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1364" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31744,6 +31744,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1365" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31767,6 +31767,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1366" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31790,6 +31790,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1367" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31813,6 +31813,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1368" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31836,6 +31836,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1369" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31859,6 +31859,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1370" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31882,6 +31882,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1371" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31905,6 +31905,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1372" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31928,6 +31928,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1373" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31951,6 +31951,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1374" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -31997,6 +31997,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1376" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1376" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1376" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -32020,6 +32020,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1377" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -32043,6 +32043,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1378" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1378" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -32066,6 +32066,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1379" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1379" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40398,6 +40398,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1381">
+      <c r="A1381" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1381" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1381" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40427,6 +40427,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1382">
+      <c r="A1382" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1382" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1382" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40456,6 +40456,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1383">
+      <c r="A1383" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1383" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40485,6 +40485,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1384">
+      <c r="A1384" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1384" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40514,6 +40514,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1385">
+      <c r="A1385" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1385" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40543,6 +40543,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1386">
+      <c r="A1386" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1386" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1386" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40572,6 +40572,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1387">
+      <c r="A1387" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1387" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1387" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40601,6 +40601,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1388">
+      <c r="A1388" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1388" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ACQ.MI.xlsx
+++ b/data/ACQ.MI.xlsx
@@ -40630,6 +40630,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1389">
+      <c r="A1389" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1389" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
